--- a/printers.xlsx
+++ b/printers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\cc.ad.cchs.net\World\Home\ITD\ahlmk\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659E15C8-B7A8-4A55-ACA2-7245930B8AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5576C2-2A0F-4DC0-9D14-48BC4EADA251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17896" windowHeight="10485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Billing Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14373" uniqueCount="5738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15505" uniqueCount="6182">
   <si>
     <t>Serial</t>
   </si>
@@ -17251,6 +17251,1338 @@
   </si>
   <si>
     <t>D32310</t>
+  </si>
+  <si>
+    <t>CNDY288746</t>
+  </si>
+  <si>
+    <t>JJSouth</t>
+  </si>
+  <si>
+    <t>JJ5-210A</t>
+  </si>
+  <si>
+    <t>D02445</t>
+  </si>
+  <si>
+    <t>PAAA004014</t>
+  </si>
+  <si>
+    <t>B14684</t>
+  </si>
+  <si>
+    <t>JJ5-501F</t>
+  </si>
+  <si>
+    <t>D02858</t>
+  </si>
+  <si>
+    <t>NLLA500921</t>
+  </si>
+  <si>
+    <t>B9886</t>
+  </si>
+  <si>
+    <t>JJ5-402</t>
+  </si>
+  <si>
+    <t>D03550</t>
+  </si>
+  <si>
+    <t>PAAA004021</t>
+  </si>
+  <si>
+    <t>B14685</t>
+  </si>
+  <si>
+    <t>JJ6-302</t>
+  </si>
+  <si>
+    <t>D03720</t>
+  </si>
+  <si>
+    <t>NLLA002644</t>
+  </si>
+  <si>
+    <t>B12024</t>
+  </si>
+  <si>
+    <t>JJ6-207</t>
+  </si>
+  <si>
+    <t>D04156</t>
+  </si>
+  <si>
+    <t>nlla005268</t>
+  </si>
+  <si>
+    <t>B9041</t>
+  </si>
+  <si>
+    <t>JJ5-301F</t>
+  </si>
+  <si>
+    <t>D05471</t>
+  </si>
+  <si>
+    <t>2AD07791</t>
+  </si>
+  <si>
+    <t>B7917</t>
+  </si>
+  <si>
+    <t>D07937</t>
+  </si>
+  <si>
+    <t>JPBCKDL1HQ</t>
+  </si>
+  <si>
+    <t>JJ6-508</t>
+  </si>
+  <si>
+    <t>D11210</t>
+  </si>
+  <si>
+    <t>CNDY446831</t>
+  </si>
+  <si>
+    <t>JJ6-305E</t>
+  </si>
+  <si>
+    <t>D11238</t>
+  </si>
+  <si>
+    <t>CNDY393298</t>
+  </si>
+  <si>
+    <t>JJ6-507H</t>
+  </si>
+  <si>
+    <t>D11241</t>
+  </si>
+  <si>
+    <t>CNGS206531</t>
+  </si>
+  <si>
+    <t>803</t>
+  </si>
+  <si>
+    <t>D11533</t>
+  </si>
+  <si>
+    <t>CNHC59W0BP</t>
+  </si>
+  <si>
+    <t>D11550</t>
+  </si>
+  <si>
+    <t>NGDA500066</t>
+  </si>
+  <si>
+    <t>B9933</t>
+  </si>
+  <si>
+    <t>D11557</t>
+  </si>
+  <si>
+    <t>CNGRH20399</t>
+  </si>
+  <si>
+    <t>JJNorth</t>
+  </si>
+  <si>
+    <t>D11562</t>
+  </si>
+  <si>
+    <t>Marketing and Communications</t>
+  </si>
+  <si>
+    <t>CNGXF29473</t>
+  </si>
+  <si>
+    <t>D11563</t>
+  </si>
+  <si>
+    <t>USBXN30537</t>
+  </si>
+  <si>
+    <t>802a</t>
+  </si>
+  <si>
+    <t>D11567</t>
+  </si>
+  <si>
+    <t>CNHC6440L8</t>
+  </si>
+  <si>
+    <t>807B</t>
+  </si>
+  <si>
+    <t>D11584</t>
+  </si>
+  <si>
+    <t>Bioethics</t>
+  </si>
+  <si>
+    <t>CNBJN80476</t>
+  </si>
+  <si>
+    <t>D11589</t>
+  </si>
+  <si>
+    <t>CNDY248617</t>
+  </si>
+  <si>
+    <t>431</t>
+  </si>
+  <si>
+    <t>D11590</t>
+  </si>
+  <si>
+    <t>CNDY267364</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>D11591</t>
+  </si>
+  <si>
+    <t>CNLKY61741</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>D11593</t>
+  </si>
+  <si>
+    <t>USBB367357</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>D11595</t>
+  </si>
+  <si>
+    <t>USGNH01523</t>
+  </si>
+  <si>
+    <t>D11596</t>
+  </si>
+  <si>
+    <t>USGW009456</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>D11597</t>
+  </si>
+  <si>
+    <t>VND3C17679</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>D11598</t>
+  </si>
+  <si>
+    <t>CN823F710V04CY</t>
+  </si>
+  <si>
+    <t>HP-OfficeJet 5610</t>
+  </si>
+  <si>
+    <t>D11599</t>
+  </si>
+  <si>
+    <t>CNUC5960SY</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>D11672</t>
+  </si>
+  <si>
+    <t>CNJ1G06932</t>
+  </si>
+  <si>
+    <t>703E</t>
+  </si>
+  <si>
+    <t>D12860</t>
+  </si>
+  <si>
+    <t>NGDA006726</t>
+  </si>
+  <si>
+    <t>B17567</t>
+  </si>
+  <si>
+    <t>JJ5-406</t>
+  </si>
+  <si>
+    <t>D12931</t>
+  </si>
+  <si>
+    <t>CNDY446897</t>
+  </si>
+  <si>
+    <t>JJ6-209</t>
+  </si>
+  <si>
+    <t>D12937</t>
+  </si>
+  <si>
+    <t>CNDY446902</t>
+  </si>
+  <si>
+    <t>JJ6-211</t>
+  </si>
+  <si>
+    <t>D12938</t>
+  </si>
+  <si>
+    <t>NRSA002699</t>
+  </si>
+  <si>
+    <t>B12762</t>
+  </si>
+  <si>
+    <t>JJ6-303</t>
+  </si>
+  <si>
+    <t>D12939</t>
+  </si>
+  <si>
+    <t>CNGXF72492</t>
+  </si>
+  <si>
+    <t>D12941</t>
+  </si>
+  <si>
+    <t>CNGXD91299</t>
+  </si>
+  <si>
+    <t>JJ6-304</t>
+  </si>
+  <si>
+    <t>D12942</t>
+  </si>
+  <si>
+    <t>CNDY449717</t>
+  </si>
+  <si>
+    <t>JJ5-801i</t>
+  </si>
+  <si>
+    <t>D12943</t>
+  </si>
+  <si>
+    <t>CNDY447476</t>
+  </si>
+  <si>
+    <t>JJ6-503</t>
+  </si>
+  <si>
+    <t>D12944</t>
+  </si>
+  <si>
+    <t>USGW138246</t>
+  </si>
+  <si>
+    <t>JJ5-505</t>
+  </si>
+  <si>
+    <t>D12949</t>
+  </si>
+  <si>
+    <t>CNBF336580</t>
+  </si>
+  <si>
+    <t>JJN6-430</t>
+  </si>
+  <si>
+    <t>D13191</t>
+  </si>
+  <si>
+    <t>Chief of Staff</t>
+  </si>
+  <si>
+    <t>OPSA</t>
+  </si>
+  <si>
+    <t>CNWBB58181</t>
+  </si>
+  <si>
+    <t>JJ6-509</t>
+  </si>
+  <si>
+    <t>D13984</t>
+  </si>
+  <si>
+    <t>CNDY299044</t>
+  </si>
+  <si>
+    <t>609</t>
+  </si>
+  <si>
+    <t>D14816</t>
+  </si>
+  <si>
+    <t>2YJ13694</t>
+  </si>
+  <si>
+    <t>B13183</t>
+  </si>
+  <si>
+    <t>JJN4-271</t>
+  </si>
+  <si>
+    <t>D16508</t>
+  </si>
+  <si>
+    <t>MARKETING</t>
+  </si>
+  <si>
+    <t>2xk04709</t>
+  </si>
+  <si>
+    <t>b13514</t>
+  </si>
+  <si>
+    <t>JJN6-441 Strategy Office</t>
+  </si>
+  <si>
+    <t>D16771</t>
+  </si>
+  <si>
+    <t>2YJ19105</t>
+  </si>
+  <si>
+    <t>B14004</t>
+  </si>
+  <si>
+    <t>JJN5-438</t>
+  </si>
+  <si>
+    <t>D16785</t>
+  </si>
+  <si>
+    <t>2YJ12606</t>
+  </si>
+  <si>
+    <t>B13182</t>
+  </si>
+  <si>
+    <t>JJ3-208</t>
+  </si>
+  <si>
+    <t>D16786</t>
+  </si>
+  <si>
+    <t>2yj15653</t>
+  </si>
+  <si>
+    <t>b13499</t>
+  </si>
+  <si>
+    <t>JJN6-318</t>
+  </si>
+  <si>
+    <t>D16794</t>
+  </si>
+  <si>
+    <t>3LN01500</t>
+  </si>
+  <si>
+    <t>B12929</t>
+  </si>
+  <si>
+    <t>JJN5-290</t>
+  </si>
+  <si>
+    <t>D16798</t>
+  </si>
+  <si>
+    <t>2YJ13727</t>
+  </si>
+  <si>
+    <t>B13186</t>
+  </si>
+  <si>
+    <t>JJS4-407A</t>
+  </si>
+  <si>
+    <t>D17093</t>
+  </si>
+  <si>
+    <t>35A32112</t>
+  </si>
+  <si>
+    <t>B14177</t>
+  </si>
+  <si>
+    <t>JJ4-511</t>
+  </si>
+  <si>
+    <t>D17183</t>
+  </si>
+  <si>
+    <t>RZJ16458</t>
+  </si>
+  <si>
+    <t>B5502</t>
+  </si>
+  <si>
+    <t>D17188</t>
+  </si>
+  <si>
+    <t>23d14981</t>
+  </si>
+  <si>
+    <t>b12554</t>
+  </si>
+  <si>
+    <t>JJN4-436</t>
+  </si>
+  <si>
+    <t>D17350</t>
+  </si>
+  <si>
+    <t>COLORECTAL</t>
+  </si>
+  <si>
+    <t>4AQ00853</t>
+  </si>
+  <si>
+    <t>B11546</t>
+  </si>
+  <si>
+    <t>JJN6-311</t>
+  </si>
+  <si>
+    <t>D17351</t>
+  </si>
+  <si>
+    <t>23E04248</t>
+  </si>
+  <si>
+    <t>B14262</t>
+  </si>
+  <si>
+    <t>JJNB-440</t>
+  </si>
+  <si>
+    <t>D17354</t>
+  </si>
+  <si>
+    <t>23d14999</t>
+  </si>
+  <si>
+    <t>b12553</t>
+  </si>
+  <si>
+    <t>JJ6-703</t>
+  </si>
+  <si>
+    <t>D17355</t>
+  </si>
+  <si>
+    <t>25V07991</t>
+  </si>
+  <si>
+    <t>B17141</t>
+  </si>
+  <si>
+    <t>Canon-IR-ADV 4745</t>
+  </si>
+  <si>
+    <t>JJNB-230</t>
+  </si>
+  <si>
+    <t>D17361</t>
+  </si>
+  <si>
+    <t>23D14848</t>
+  </si>
+  <si>
+    <t>B12557</t>
+  </si>
+  <si>
+    <t>JJN3-440 Biostatistics</t>
+  </si>
+  <si>
+    <t>D17366</t>
+  </si>
+  <si>
+    <t>35A32031</t>
+  </si>
+  <si>
+    <t>B14116</t>
+  </si>
+  <si>
+    <t>JJN4-410</t>
+  </si>
+  <si>
+    <t>D17443</t>
+  </si>
+  <si>
+    <t>3LN01857</t>
+  </si>
+  <si>
+    <t>B12954</t>
+  </si>
+  <si>
+    <t>JJN1-517</t>
+  </si>
+  <si>
+    <t>D17486</t>
+  </si>
+  <si>
+    <t>38M02225</t>
+  </si>
+  <si>
+    <t>B10702</t>
+  </si>
+  <si>
+    <t>JJN1-200 Copy Room</t>
+  </si>
+  <si>
+    <t>D17490</t>
+  </si>
+  <si>
+    <t>3CE11388</t>
+  </si>
+  <si>
+    <t>B12723</t>
+  </si>
+  <si>
+    <t>JJN1-290</t>
+  </si>
+  <si>
+    <t>D17491</t>
+  </si>
+  <si>
+    <t>23E04113</t>
+  </si>
+  <si>
+    <t>B14336</t>
+  </si>
+  <si>
+    <t>JJ5-209</t>
+  </si>
+  <si>
+    <t>D17499</t>
+  </si>
+  <si>
+    <t>23d14184</t>
+  </si>
+  <si>
+    <t>b12547</t>
+  </si>
+  <si>
+    <t>JJ6-507D</t>
+  </si>
+  <si>
+    <t>D17501</t>
+  </si>
+  <si>
+    <t>23D14175</t>
+  </si>
+  <si>
+    <t>B12551</t>
+  </si>
+  <si>
+    <t>JJ4-204</t>
+  </si>
+  <si>
+    <t>D17945</t>
+  </si>
+  <si>
+    <t>3LP00894</t>
+  </si>
+  <si>
+    <t>b13155</t>
+  </si>
+  <si>
+    <t>JJ1-201</t>
+  </si>
+  <si>
+    <t>D18096</t>
+  </si>
+  <si>
+    <t>35A04191</t>
+  </si>
+  <si>
+    <t>B12815</t>
+  </si>
+  <si>
+    <t>JJN4-434</t>
+  </si>
+  <si>
+    <t>D18142</t>
+  </si>
+  <si>
+    <t>3GE06045</t>
+  </si>
+  <si>
+    <t>B15152</t>
+  </si>
+  <si>
+    <t>JJN5-331</t>
+  </si>
+  <si>
+    <t>D18191</t>
+  </si>
+  <si>
+    <t>23D33015</t>
+  </si>
+  <si>
+    <t>B15089</t>
+  </si>
+  <si>
+    <t>JJNB-400 Badging-Front Desk</t>
+  </si>
+  <si>
+    <t>D18335</t>
+  </si>
+  <si>
+    <t>2YJ28621</t>
+  </si>
+  <si>
+    <t>B15788</t>
+  </si>
+  <si>
+    <t>JJ1-609</t>
+  </si>
+  <si>
+    <t>D18551</t>
+  </si>
+  <si>
+    <t>2YJ28624</t>
+  </si>
+  <si>
+    <t>B15789</t>
+  </si>
+  <si>
+    <t>JJ1-805 - Back Office</t>
+  </si>
+  <si>
+    <t>D18552</t>
+  </si>
+  <si>
+    <t>3CE10906</t>
+  </si>
+  <si>
+    <t>B12184</t>
+  </si>
+  <si>
+    <t>JJN3-271 Quantitative Health Science</t>
+  </si>
+  <si>
+    <t>D18593</t>
+  </si>
+  <si>
+    <t>QHS</t>
+  </si>
+  <si>
+    <t>3GE06066</t>
+  </si>
+  <si>
+    <t>B15187</t>
+  </si>
+  <si>
+    <t>JJNB-450 Protective Services Administration</t>
+  </si>
+  <si>
+    <t>D18713</t>
+  </si>
+  <si>
+    <t>CND1N00301</t>
+  </si>
+  <si>
+    <t>JJ6-306</t>
+  </si>
+  <si>
+    <t>D20687</t>
+  </si>
+  <si>
+    <t>CNGS702011</t>
+  </si>
+  <si>
+    <t>D22332</t>
+  </si>
+  <si>
+    <t>CNB0508077</t>
+  </si>
+  <si>
+    <t>JJ6-202</t>
+  </si>
+  <si>
+    <t>D22352</t>
+  </si>
+  <si>
+    <t>VNB3H66677</t>
+  </si>
+  <si>
+    <t>D22355</t>
+  </si>
+  <si>
+    <t>CNC8333323</t>
+  </si>
+  <si>
+    <t>JJ5-508</t>
+  </si>
+  <si>
+    <t>D22356</t>
+  </si>
+  <si>
+    <t>USBB386134</t>
+  </si>
+  <si>
+    <t>JJ5-606</t>
+  </si>
+  <si>
+    <t>D22357</t>
+  </si>
+  <si>
+    <t>USMC090044</t>
+  </si>
+  <si>
+    <t>JJ6-206</t>
+  </si>
+  <si>
+    <t>D22361</t>
+  </si>
+  <si>
+    <t>CNGXH03625</t>
+  </si>
+  <si>
+    <t>JJ6-505</t>
+  </si>
+  <si>
+    <t>D22365</t>
+  </si>
+  <si>
+    <t>USMC061255</t>
+  </si>
+  <si>
+    <t>JJ6-406</t>
+  </si>
+  <si>
+    <t>D22366</t>
+  </si>
+  <si>
+    <t>USCC045912</t>
+  </si>
+  <si>
+    <t>JJ6-502</t>
+  </si>
+  <si>
+    <t>D22368</t>
+  </si>
+  <si>
+    <t>USCB024868</t>
+  </si>
+  <si>
+    <t>D22369</t>
+  </si>
+  <si>
+    <t>38M01417</t>
+  </si>
+  <si>
+    <t>B10701</t>
+  </si>
+  <si>
+    <t>D22393</t>
+  </si>
+  <si>
+    <t>USMB254717</t>
+  </si>
+  <si>
+    <t>JJ5-203C</t>
+  </si>
+  <si>
+    <t>D22468</t>
+  </si>
+  <si>
+    <t>CND1H12746</t>
+  </si>
+  <si>
+    <t>JJN5-274</t>
+  </si>
+  <si>
+    <t>D22539</t>
+  </si>
+  <si>
+    <t>00237d882ef2</t>
+  </si>
+  <si>
+    <t>JJ6-810</t>
+  </si>
+  <si>
+    <t>D22595</t>
+  </si>
+  <si>
+    <t>CNDCH1M057</t>
+  </si>
+  <si>
+    <t>710</t>
+  </si>
+  <si>
+    <t>D22597</t>
+  </si>
+  <si>
+    <t>CNB0208470</t>
+  </si>
+  <si>
+    <t>D22652</t>
+  </si>
+  <si>
+    <t>VNB3L26164</t>
+  </si>
+  <si>
+    <t>D22670</t>
+  </si>
+  <si>
+    <t>CNB9G09434</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>D23329</t>
+  </si>
+  <si>
+    <t>4QS03884</t>
+  </si>
+  <si>
+    <t>B14254</t>
+  </si>
+  <si>
+    <t>JJN6-470</t>
+  </si>
+  <si>
+    <t>D23547</t>
+  </si>
+  <si>
+    <t>3BN06746</t>
+  </si>
+  <si>
+    <t>B9195</t>
+  </si>
+  <si>
+    <t>JJN2-350</t>
+  </si>
+  <si>
+    <t>D23575</t>
+  </si>
+  <si>
+    <t>ngda006629</t>
+  </si>
+  <si>
+    <t>B9166</t>
+  </si>
+  <si>
+    <t>209J</t>
+  </si>
+  <si>
+    <t>D23732</t>
+  </si>
+  <si>
+    <t>Cardio-Thoracic</t>
+  </si>
+  <si>
+    <t>CNDCGBF27M</t>
+  </si>
+  <si>
+    <t>HP-LaserJet 500 Color M570dn</t>
+  </si>
+  <si>
+    <t>D23918</t>
+  </si>
+  <si>
+    <t>CNCCF5DOK6</t>
+  </si>
+  <si>
+    <t>805</t>
+  </si>
+  <si>
+    <t>D23921</t>
+  </si>
+  <si>
+    <t>2yj14765</t>
+  </si>
+  <si>
+    <t>b13493</t>
+  </si>
+  <si>
+    <t>JJS4-607</t>
+  </si>
+  <si>
+    <t>D23981</t>
+  </si>
+  <si>
+    <t>3CE11019</t>
+  </si>
+  <si>
+    <t>B12724</t>
+  </si>
+  <si>
+    <t>JJN2-435</t>
+  </si>
+  <si>
+    <t>D24019</t>
+  </si>
+  <si>
+    <t>3CE11572</t>
+  </si>
+  <si>
+    <t>B12722</t>
+  </si>
+  <si>
+    <t>JJN2-537</t>
+  </si>
+  <si>
+    <t>D24020</t>
+  </si>
+  <si>
+    <t>3CE11386</t>
+  </si>
+  <si>
+    <t>B12812</t>
+  </si>
+  <si>
+    <t>JJN2-244</t>
+  </si>
+  <si>
+    <t>D24021</t>
+  </si>
+  <si>
+    <t>4QS01099</t>
+  </si>
+  <si>
+    <t>B13629</t>
+  </si>
+  <si>
+    <t>JJN2-0439</t>
+  </si>
+  <si>
+    <t>D24023</t>
+  </si>
+  <si>
+    <t>VNB3D06558</t>
+  </si>
+  <si>
+    <t>803C</t>
+  </si>
+  <si>
+    <t>D24074</t>
+  </si>
+  <si>
+    <t>Strategy Office</t>
+  </si>
+  <si>
+    <t>VNDAC32123</t>
+  </si>
+  <si>
+    <t>803A</t>
+  </si>
+  <si>
+    <t>D24097</t>
+  </si>
+  <si>
+    <t>VND3C32126</t>
+  </si>
+  <si>
+    <t>803F</t>
+  </si>
+  <si>
+    <t>D24098</t>
+  </si>
+  <si>
+    <t>VNB3G55360</t>
+  </si>
+  <si>
+    <t>803E</t>
+  </si>
+  <si>
+    <t>D24099</t>
+  </si>
+  <si>
+    <t>VNB3L93212</t>
+  </si>
+  <si>
+    <t>803G</t>
+  </si>
+  <si>
+    <t>D24100</t>
+  </si>
+  <si>
+    <t>VND3F04099</t>
+  </si>
+  <si>
+    <t>803H</t>
+  </si>
+  <si>
+    <t>D24121</t>
+  </si>
+  <si>
+    <t>VND3C32128</t>
+  </si>
+  <si>
+    <t>801D</t>
+  </si>
+  <si>
+    <t>D24123</t>
+  </si>
+  <si>
+    <t>CNCCB4L1K2</t>
+  </si>
+  <si>
+    <t>801C</t>
+  </si>
+  <si>
+    <t>D24124</t>
+  </si>
+  <si>
+    <t>JP4LB32745</t>
+  </si>
+  <si>
+    <t>D24175</t>
+  </si>
+  <si>
+    <t>2YJ19093</t>
+  </si>
+  <si>
+    <t>B14006</t>
+  </si>
+  <si>
+    <t>263</t>
+  </si>
+  <si>
+    <t>D24192</t>
+  </si>
+  <si>
+    <t>cnrk265129</t>
+  </si>
+  <si>
+    <t>D24371</t>
+  </si>
+  <si>
+    <t>CNBGB80159</t>
+  </si>
+  <si>
+    <t>D24384</t>
+  </si>
+  <si>
+    <t>23d14172</t>
+  </si>
+  <si>
+    <t>b12549</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>D24397</t>
+  </si>
+  <si>
+    <t>4JB07018</t>
+  </si>
+  <si>
+    <t>B15998</t>
+  </si>
+  <si>
+    <t>D24401</t>
+  </si>
+  <si>
+    <t>2YJ13649</t>
+  </si>
+  <si>
+    <t>B13179</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>D24402</t>
+  </si>
+  <si>
+    <t>23E03077</t>
+  </si>
+  <si>
+    <t>B13565</t>
+  </si>
+  <si>
+    <t>D24617</t>
+  </si>
+  <si>
+    <t>23d14720</t>
+  </si>
+  <si>
+    <t>b12550</t>
+  </si>
+  <si>
+    <t>JJ6-210A</t>
+  </si>
+  <si>
+    <t>D24618</t>
+  </si>
+  <si>
+    <t>3CE10869</t>
+  </si>
+  <si>
+    <t>B12819</t>
+  </si>
+  <si>
+    <t>D24690</t>
+  </si>
+  <si>
+    <t>2YJ13943</t>
+  </si>
+  <si>
+    <t>B13184</t>
+  </si>
+  <si>
+    <t>JJ5-504</t>
+  </si>
+  <si>
+    <t>D24883</t>
+  </si>
+  <si>
+    <t>CNCCFDM00X</t>
+  </si>
+  <si>
+    <t>D24900</t>
+  </si>
+  <si>
+    <t>2YJ13731</t>
+  </si>
+  <si>
+    <t>B13185</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>D26548</t>
+  </si>
+  <si>
+    <t>35A36122</t>
+  </si>
+  <si>
+    <t>B14986</t>
+  </si>
+  <si>
+    <t>JJS-100</t>
+  </si>
+  <si>
+    <t>D26561</t>
+  </si>
+  <si>
+    <t>NLLA502167</t>
+  </si>
+  <si>
+    <t>B12732</t>
+  </si>
+  <si>
+    <t>D26672</t>
+  </si>
+  <si>
+    <t>XUW08803</t>
+  </si>
+  <si>
+    <t>B14355</t>
+  </si>
+  <si>
+    <t>JJN3-440</t>
+  </si>
+  <si>
+    <t>D28374</t>
+  </si>
+  <si>
+    <t>PAAA005894</t>
+  </si>
+  <si>
+    <t>B16693</t>
+  </si>
+  <si>
+    <t>D29210</t>
+  </si>
+  <si>
+    <t>NGDA007998</t>
+  </si>
+  <si>
+    <t>B8883</t>
+  </si>
+  <si>
+    <t>JJS6-209A</t>
+  </si>
+  <si>
+    <t>D31046</t>
+  </si>
+  <si>
+    <t>4JB07537</t>
+  </si>
+  <si>
+    <t>B16266</t>
+  </si>
+  <si>
+    <t>JJS3-801B</t>
+  </si>
+  <si>
+    <t>D33521</t>
+  </si>
+  <si>
+    <t>3kg03525</t>
+  </si>
+  <si>
+    <t>b12166</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>D35214</t>
+  </si>
+  <si>
+    <t>2YJ38254</t>
+  </si>
+  <si>
+    <t>B17277</t>
+  </si>
+  <si>
+    <t>JJS3-701</t>
+  </si>
+  <si>
+    <t>D37438</t>
+  </si>
+  <si>
+    <t>CNBF336397</t>
+  </si>
+  <si>
+    <t>D40249</t>
+  </si>
+  <si>
+    <t>CNGKC10343</t>
+  </si>
+  <si>
+    <t>D40251</t>
+  </si>
+  <si>
+    <t>CNDXC04665</t>
+  </si>
+  <si>
+    <t>HP-LaserJet 5200</t>
+  </si>
+  <si>
+    <t>D40255</t>
   </si>
 </sst>
 </file>
@@ -17261,7 +18593,7 @@
     <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     <numFmt numFmtId="165" formatCode="\$###,###,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -17272,6 +18604,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -17295,10 +18632,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17340,8 +18680,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D20A6D39-A2BB-4955-B43F-906CB16A1B26}" name="Table1" displayName="Table1" ref="A1:L1599" totalsRowShown="0" headerRowDxfId="6">
-  <autoFilter ref="A1:L1599" xr:uid="{D20A6D39-A2BB-4955-B43F-906CB16A1B26}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D20A6D39-A2BB-4955-B43F-906CB16A1B26}" name="Table1" displayName="Table1" ref="A1:L1730" totalsRowShown="0" headerRowDxfId="6">
+  <autoFilter ref="A1:L1730" xr:uid="{D20A6D39-A2BB-4955-B43F-906CB16A1B26}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{26695ECC-C4BD-42BA-86A4-CDD3C6CEE68E}" name="Serial"/>
     <tableColumn id="2" xr3:uid="{DF1DE3F8-F611-4EEB-8B06-9803B6A4C593}" name="Bnumber"/>
@@ -17352,9 +18692,9 @@
     <tableColumn id="13" xr3:uid="{EC368605-3EF2-4D0A-8AC4-7CB29770D35F}" name="LeaseEnd" dataDxfId="4"/>
     <tableColumn id="18" xr3:uid="{CD98533F-E6D4-475E-A7FE-AB47037BE125}" name="AvgPagesPrinted"/>
     <tableColumn id="20" xr3:uid="{F43F8E1F-336D-479F-828C-AFFE60BD4066}" name="Dnumber" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{D32632F4-CFE1-4C03-909B-75AE0765D853}" name="Epic" dataDxfId="0"/>
-    <tableColumn id="22" xr3:uid="{AF9A5037-879A-4F50-9648-D64CCDBCEEF6}" name="Institute" dataDxfId="2"/>
-    <tableColumn id="23" xr3:uid="{B0D53022-F6DF-426B-9DEA-E1CE97B82C97}" name="Department" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{D32632F4-CFE1-4C03-909B-75AE0765D853}" name="Epic" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{AF9A5037-879A-4F50-9648-D64CCDBCEEF6}" name="Institute" dataDxfId="1"/>
+    <tableColumn id="23" xr3:uid="{B0D53022-F6DF-426B-9DEA-E1CE97B82C97}" name="Department" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17677,7 +19017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1599"/>
+  <dimension ref="A1:L1730"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.86328125" bestFit="1" customWidth="1"/>
@@ -76668,6 +78008,4688 @@
         <v>906</v>
       </c>
     </row>
+    <row r="1600" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1600" t="s">
+        <v>5738</v>
+      </c>
+      <c r="C1600" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1600" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1600" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1600" t="s">
+        <v>5740</v>
+      </c>
+      <c r="G1600" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1600">
+        <v>0</v>
+      </c>
+      <c r="I1600" s="4" t="s">
+        <v>5741</v>
+      </c>
+      <c r="J1600" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1600" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1600" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1601" t="s">
+        <v>5742</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>5743</v>
+      </c>
+      <c r="C1601" s="4" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1601" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1601" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1601" t="s">
+        <v>5744</v>
+      </c>
+      <c r="G1601" s="1">
+        <v>46966</v>
+      </c>
+      <c r="H1601">
+        <v>3889</v>
+      </c>
+      <c r="I1601" s="4" t="s">
+        <v>5745</v>
+      </c>
+      <c r="J1601" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1601" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1601" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1602" t="s">
+        <v>5746</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>5747</v>
+      </c>
+      <c r="C1602" s="4" t="s">
+        <v>3849</v>
+      </c>
+      <c r="D1602" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1602" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1602" s="3" t="s">
+        <v>5748</v>
+      </c>
+      <c r="G1602" s="1">
+        <v>46327</v>
+      </c>
+      <c r="H1602">
+        <v>6198</v>
+      </c>
+      <c r="I1602" s="4" t="s">
+        <v>5749</v>
+      </c>
+      <c r="J1602" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1602" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1602" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1603" t="s">
+        <v>5750</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>5751</v>
+      </c>
+      <c r="C1603" s="4" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1603" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1603" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1603" t="s">
+        <v>5752</v>
+      </c>
+      <c r="G1603" s="1">
+        <v>46966</v>
+      </c>
+      <c r="H1603">
+        <v>835</v>
+      </c>
+      <c r="I1603" s="4" t="s">
+        <v>5753</v>
+      </c>
+      <c r="J1603" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1603" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1603" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1604" t="s">
+        <v>5754</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>5755</v>
+      </c>
+      <c r="C1604" s="4" t="s">
+        <v>3849</v>
+      </c>
+      <c r="D1604" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1604" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1604" t="s">
+        <v>5756</v>
+      </c>
+      <c r="G1604" s="1">
+        <v>46023</v>
+      </c>
+      <c r="H1604">
+        <v>361</v>
+      </c>
+      <c r="I1604" s="4" t="s">
+        <v>5757</v>
+      </c>
+      <c r="J1604" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1604" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1604" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1605" t="s">
+        <v>5758</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>5759</v>
+      </c>
+      <c r="C1605" s="4" t="s">
+        <v>3849</v>
+      </c>
+      <c r="D1605" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1605" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1605" t="s">
+        <v>5760</v>
+      </c>
+      <c r="G1605" s="1">
+        <v>46204</v>
+      </c>
+      <c r="H1605">
+        <v>3148</v>
+      </c>
+      <c r="I1605" s="4" t="s">
+        <v>5761</v>
+      </c>
+      <c r="J1605" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1605" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1605" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1606" t="s">
+        <v>5762</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>5763</v>
+      </c>
+      <c r="C1606" s="4" t="s">
+        <v>3917</v>
+      </c>
+      <c r="D1606" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1606" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1606" t="s">
+        <v>348</v>
+      </c>
+      <c r="G1606" s="1">
+        <v>46023</v>
+      </c>
+      <c r="H1606">
+        <v>147</v>
+      </c>
+      <c r="I1606" s="4" t="s">
+        <v>5764</v>
+      </c>
+      <c r="J1606" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1606" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1606" s="4" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1607" t="s">
+        <v>5765</v>
+      </c>
+      <c r="C1607" s="4" t="s">
+        <v>3934</v>
+      </c>
+      <c r="D1607" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1607" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1607" t="s">
+        <v>5766</v>
+      </c>
+      <c r="G1607" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1607">
+        <v>137</v>
+      </c>
+      <c r="I1607" s="4" t="s">
+        <v>5767</v>
+      </c>
+      <c r="J1607" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1607" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1607" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1608" t="s">
+        <v>5768</v>
+      </c>
+      <c r="C1608" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1608" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1608" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1608" t="s">
+        <v>5769</v>
+      </c>
+      <c r="G1608" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1608">
+        <v>0</v>
+      </c>
+      <c r="I1608" s="4" t="s">
+        <v>5770</v>
+      </c>
+      <c r="J1608" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1608" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1608" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1609" t="s">
+        <v>5771</v>
+      </c>
+      <c r="C1609" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1609" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1609" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1609" t="s">
+        <v>5772</v>
+      </c>
+      <c r="G1609" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1609">
+        <v>0</v>
+      </c>
+      <c r="I1609" s="4" t="s">
+        <v>5773</v>
+      </c>
+      <c r="J1609" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1609" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1609" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1610" t="s">
+        <v>5774</v>
+      </c>
+      <c r="C1610" s="4" t="s">
+        <v>3930</v>
+      </c>
+      <c r="D1610" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1610" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1610" t="s">
+        <v>5775</v>
+      </c>
+      <c r="G1610" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1610">
+        <v>0</v>
+      </c>
+      <c r="I1610" s="4" t="s">
+        <v>5776</v>
+      </c>
+      <c r="J1610" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1610" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1610" s="4"/>
+    </row>
+    <row r="1611" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1611" t="s">
+        <v>5777</v>
+      </c>
+      <c r="C1611" s="4" t="s">
+        <v>3872</v>
+      </c>
+      <c r="D1611" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1611" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1611" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1611" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1611">
+        <v>0</v>
+      </c>
+      <c r="I1611" s="4" t="s">
+        <v>5778</v>
+      </c>
+      <c r="J1611" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1611" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1611" s="4"/>
+    </row>
+    <row r="1612" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1612" t="s">
+        <v>5779</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>5780</v>
+      </c>
+      <c r="C1612" s="4" t="s">
+        <v>3865</v>
+      </c>
+      <c r="D1612" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1612" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1612" t="s">
+        <v>638</v>
+      </c>
+      <c r="G1612" s="1">
+        <v>46357</v>
+      </c>
+      <c r="H1612">
+        <v>831</v>
+      </c>
+      <c r="I1612" s="4" t="s">
+        <v>5781</v>
+      </c>
+      <c r="J1612" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1612" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1612" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1613" t="s">
+        <v>5782</v>
+      </c>
+      <c r="C1613" s="4" t="s">
+        <v>3887</v>
+      </c>
+      <c r="D1613" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1613" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1613" t="s">
+        <v>348</v>
+      </c>
+      <c r="G1613" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1613">
+        <v>0</v>
+      </c>
+      <c r="I1613" s="4" t="s">
+        <v>5784</v>
+      </c>
+      <c r="J1613" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1613" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1613" s="4" t="s">
+        <v>5785</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1614" t="s">
+        <v>5786</v>
+      </c>
+      <c r="C1614" s="4" t="s">
+        <v>3853</v>
+      </c>
+      <c r="D1614" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1614" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1614" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1614" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1614">
+        <v>0</v>
+      </c>
+      <c r="I1614" s="4" t="s">
+        <v>5787</v>
+      </c>
+      <c r="J1614" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1614" s="4"/>
+      <c r="L1614" s="4"/>
+    </row>
+    <row r="1615" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1615" t="s">
+        <v>5788</v>
+      </c>
+      <c r="C1615" s="4" t="s">
+        <v>3853</v>
+      </c>
+      <c r="D1615" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1615" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1615" t="s">
+        <v>5789</v>
+      </c>
+      <c r="G1615" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1615">
+        <v>0</v>
+      </c>
+      <c r="I1615" s="4" t="s">
+        <v>5790</v>
+      </c>
+      <c r="J1615" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1615" s="4"/>
+      <c r="L1615" s="4"/>
+    </row>
+    <row r="1616" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1616" t="s">
+        <v>5791</v>
+      </c>
+      <c r="C1616" s="4" t="s">
+        <v>3872</v>
+      </c>
+      <c r="D1616" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1616" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1616" t="s">
+        <v>5792</v>
+      </c>
+      <c r="G1616" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1616">
+        <v>0</v>
+      </c>
+      <c r="I1616" s="4" t="s">
+        <v>5793</v>
+      </c>
+      <c r="J1616" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1616" s="4"/>
+      <c r="L1616" s="4" t="s">
+        <v>5794</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1617" t="s">
+        <v>5795</v>
+      </c>
+      <c r="C1617" s="4" t="s">
+        <v>3916</v>
+      </c>
+      <c r="D1617" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1617" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1617" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1617" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1617">
+        <v>0</v>
+      </c>
+      <c r="I1617" s="4" t="s">
+        <v>5796</v>
+      </c>
+      <c r="J1617" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1617" s="4"/>
+      <c r="L1617" s="4"/>
+    </row>
+    <row r="1618" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1618" t="s">
+        <v>5797</v>
+      </c>
+      <c r="C1618" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1618" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1618" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1618" t="s">
+        <v>5798</v>
+      </c>
+      <c r="G1618" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1618">
+        <v>0</v>
+      </c>
+      <c r="I1618" s="4" t="s">
+        <v>5799</v>
+      </c>
+      <c r="J1618" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1618" s="4"/>
+      <c r="L1618" s="4"/>
+    </row>
+    <row r="1619" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1619" t="s">
+        <v>5800</v>
+      </c>
+      <c r="C1619" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1619" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1619" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1619" t="s">
+        <v>5801</v>
+      </c>
+      <c r="G1619" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1619">
+        <v>0</v>
+      </c>
+      <c r="I1619" s="4" t="s">
+        <v>5802</v>
+      </c>
+      <c r="J1619" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1619" s="4"/>
+      <c r="L1619" s="4"/>
+    </row>
+    <row r="1620" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1620" t="s">
+        <v>5803</v>
+      </c>
+      <c r="C1620" s="4" t="s">
+        <v>3872</v>
+      </c>
+      <c r="D1620" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1620" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1620" t="s">
+        <v>5804</v>
+      </c>
+      <c r="G1620" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1620">
+        <v>0</v>
+      </c>
+      <c r="I1620" s="4" t="s">
+        <v>5805</v>
+      </c>
+      <c r="J1620" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1620" s="4"/>
+      <c r="L1620" s="4"/>
+    </row>
+    <row r="1621" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1621" t="s">
+        <v>5806</v>
+      </c>
+      <c r="C1621" s="4" t="s">
+        <v>3901</v>
+      </c>
+      <c r="D1621" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1621" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1621" t="s">
+        <v>5807</v>
+      </c>
+      <c r="G1621" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1621">
+        <v>0</v>
+      </c>
+      <c r="I1621" s="4" t="s">
+        <v>5808</v>
+      </c>
+      <c r="J1621" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1621" s="4"/>
+      <c r="L1621" s="4"/>
+    </row>
+    <row r="1622" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1622" t="s">
+        <v>5809</v>
+      </c>
+      <c r="C1622" s="4" t="s">
+        <v>3920</v>
+      </c>
+      <c r="D1622" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1622" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1622" t="s">
+        <v>5801</v>
+      </c>
+      <c r="G1622" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1622">
+        <v>0</v>
+      </c>
+      <c r="I1622" s="4" t="s">
+        <v>5810</v>
+      </c>
+      <c r="J1622" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1622" s="4"/>
+      <c r="L1622" s="4"/>
+    </row>
+    <row r="1623" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1623" t="s">
+        <v>5811</v>
+      </c>
+      <c r="C1623" s="4" t="s">
+        <v>3856</v>
+      </c>
+      <c r="D1623" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1623" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1623" t="s">
+        <v>5812</v>
+      </c>
+      <c r="G1623" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1623">
+        <v>0</v>
+      </c>
+      <c r="I1623" s="4" t="s">
+        <v>5813</v>
+      </c>
+      <c r="J1623" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1623" s="4"/>
+      <c r="L1623" s="4"/>
+    </row>
+    <row r="1624" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1624" t="s">
+        <v>5814</v>
+      </c>
+      <c r="C1624" s="4" t="s">
+        <v>3852</v>
+      </c>
+      <c r="D1624" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1624" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1624" t="s">
+        <v>5815</v>
+      </c>
+      <c r="G1624" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1624">
+        <v>0</v>
+      </c>
+      <c r="I1624" s="4" t="s">
+        <v>5816</v>
+      </c>
+      <c r="J1624" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1624" s="4"/>
+      <c r="L1624" s="4"/>
+    </row>
+    <row r="1625" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1625" t="s">
+        <v>5817</v>
+      </c>
+      <c r="C1625" s="4" t="s">
+        <v>5818</v>
+      </c>
+      <c r="D1625" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1625" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1625" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1625" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1625">
+        <v>0</v>
+      </c>
+      <c r="I1625" s="4" t="s">
+        <v>5819</v>
+      </c>
+      <c r="J1625" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1625" s="4"/>
+      <c r="L1625" s="4"/>
+    </row>
+    <row r="1626" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1626" t="s">
+        <v>5820</v>
+      </c>
+      <c r="C1626" s="4" t="s">
+        <v>3872</v>
+      </c>
+      <c r="D1626" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1626" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1626" t="s">
+        <v>5821</v>
+      </c>
+      <c r="G1626" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1626">
+        <v>0</v>
+      </c>
+      <c r="I1626" s="4" t="s">
+        <v>5822</v>
+      </c>
+      <c r="J1626" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1626" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1626" s="4" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1627" t="s">
+        <v>5823</v>
+      </c>
+      <c r="C1627" s="4" t="s">
+        <v>3858</v>
+      </c>
+      <c r="D1627" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1627" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1627" t="s">
+        <v>5824</v>
+      </c>
+      <c r="G1627" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1627">
+        <v>0</v>
+      </c>
+      <c r="I1627" s="4" t="s">
+        <v>5825</v>
+      </c>
+      <c r="J1627" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1627" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1627" s="4" t="s">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1628" t="s">
+        <v>5826</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>5827</v>
+      </c>
+      <c r="C1628" s="4" t="s">
+        <v>3865</v>
+      </c>
+      <c r="D1628" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1628" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1628" t="s">
+        <v>5828</v>
+      </c>
+      <c r="G1628" s="1">
+        <v>46023</v>
+      </c>
+      <c r="H1628">
+        <v>237</v>
+      </c>
+      <c r="I1628" s="4" t="s">
+        <v>5829</v>
+      </c>
+      <c r="J1628" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1628" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1628" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1629" t="s">
+        <v>5830</v>
+      </c>
+      <c r="C1629" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1629" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>5831</v>
+      </c>
+      <c r="G1629" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1629">
+        <v>0</v>
+      </c>
+      <c r="I1629" s="4" t="s">
+        <v>5832</v>
+      </c>
+      <c r="J1629" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1629" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1629" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1630" t="s">
+        <v>5833</v>
+      </c>
+      <c r="C1630" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1630" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1630" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1630" t="s">
+        <v>5834</v>
+      </c>
+      <c r="G1630" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1630">
+        <v>0</v>
+      </c>
+      <c r="I1630" s="4" t="s">
+        <v>5835</v>
+      </c>
+      <c r="J1630" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1630" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1630" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1631" t="s">
+        <v>5836</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>5837</v>
+      </c>
+      <c r="C1631" s="4" t="s">
+        <v>3875</v>
+      </c>
+      <c r="D1631" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1631" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1631" t="s">
+        <v>5838</v>
+      </c>
+      <c r="G1631" s="1">
+        <v>46661</v>
+      </c>
+      <c r="H1631">
+        <v>850</v>
+      </c>
+      <c r="I1631" s="4" t="s">
+        <v>5839</v>
+      </c>
+      <c r="J1631" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1631" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1631" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1632" t="s">
+        <v>5840</v>
+      </c>
+      <c r="C1632" s="4" t="s">
+        <v>3853</v>
+      </c>
+      <c r="D1632" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1632" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1632" t="s">
+        <v>5769</v>
+      </c>
+      <c r="G1632" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1632">
+        <v>0</v>
+      </c>
+      <c r="I1632" s="4" t="s">
+        <v>5841</v>
+      </c>
+      <c r="J1632" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1632" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1632" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1633" t="s">
+        <v>5842</v>
+      </c>
+      <c r="C1633" s="4" t="s">
+        <v>3853</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1633" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1633" t="s">
+        <v>5843</v>
+      </c>
+      <c r="G1633" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1633">
+        <v>0</v>
+      </c>
+      <c r="I1633" s="4" t="s">
+        <v>5844</v>
+      </c>
+      <c r="J1633" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1633" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1633" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1634" t="s">
+        <v>5845</v>
+      </c>
+      <c r="C1634" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1634" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1634" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1634" t="s">
+        <v>5846</v>
+      </c>
+      <c r="G1634" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1634">
+        <v>0</v>
+      </c>
+      <c r="I1634" s="4" t="s">
+        <v>5847</v>
+      </c>
+      <c r="J1634" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1634" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1634" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1635" t="s">
+        <v>5848</v>
+      </c>
+      <c r="C1635" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1635" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1635" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1635" t="s">
+        <v>5849</v>
+      </c>
+      <c r="G1635" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1635">
+        <v>0</v>
+      </c>
+      <c r="I1635" s="4" t="s">
+        <v>5850</v>
+      </c>
+      <c r="J1635" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1635" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1635" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1636" t="s">
+        <v>5851</v>
+      </c>
+      <c r="C1636" s="4" t="s">
+        <v>3856</v>
+      </c>
+      <c r="D1636" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1636" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1636" t="s">
+        <v>5852</v>
+      </c>
+      <c r="G1636" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1636">
+        <v>0</v>
+      </c>
+      <c r="I1636" s="4" t="s">
+        <v>5853</v>
+      </c>
+      <c r="J1636" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1636" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1636" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1637" t="s">
+        <v>5854</v>
+      </c>
+      <c r="C1637" s="4" t="s">
+        <v>3900</v>
+      </c>
+      <c r="D1637" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1637" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1637" t="s">
+        <v>5855</v>
+      </c>
+      <c r="G1637" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1637">
+        <v>0</v>
+      </c>
+      <c r="I1637" s="4" t="s">
+        <v>5856</v>
+      </c>
+      <c r="J1637" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1637" s="4" t="s">
+        <v>5857</v>
+      </c>
+      <c r="L1637" s="4" t="s">
+        <v>5858</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1638" t="s">
+        <v>5859</v>
+      </c>
+      <c r="C1638" s="4" t="s">
+        <v>3954</v>
+      </c>
+      <c r="D1638" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1638" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1638" t="s">
+        <v>5860</v>
+      </c>
+      <c r="G1638" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1638">
+        <v>1</v>
+      </c>
+      <c r="I1638" s="4" t="s">
+        <v>5861</v>
+      </c>
+      <c r="J1638" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1638" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1638" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1639" t="s">
+        <v>5862</v>
+      </c>
+      <c r="C1639" s="4" t="s">
+        <v>3855</v>
+      </c>
+      <c r="D1639" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1639" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1639" t="s">
+        <v>5863</v>
+      </c>
+      <c r="G1639" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1639">
+        <v>0</v>
+      </c>
+      <c r="I1639" s="4" t="s">
+        <v>5864</v>
+      </c>
+      <c r="J1639" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1639" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1639" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1640" t="s">
+        <v>5865</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>5866</v>
+      </c>
+      <c r="C1640" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1640" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1640" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1640" t="s">
+        <v>5867</v>
+      </c>
+      <c r="G1640" s="1">
+        <v>46722</v>
+      </c>
+      <c r="H1640">
+        <v>768</v>
+      </c>
+      <c r="I1640" s="4" t="s">
+        <v>5868</v>
+      </c>
+      <c r="J1640" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1640" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1640" s="4" t="s">
+        <v>5869</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1641" t="s">
+        <v>5870</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>5871</v>
+      </c>
+      <c r="C1641" s="4" t="s">
+        <v>3981</v>
+      </c>
+      <c r="D1641" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1641" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1641" t="s">
+        <v>5872</v>
+      </c>
+      <c r="G1641" s="1">
+        <v>46753</v>
+      </c>
+      <c r="H1641">
+        <v>2112</v>
+      </c>
+      <c r="I1641" s="4" t="s">
+        <v>5873</v>
+      </c>
+      <c r="J1641" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1641" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1641" s="4"/>
+    </row>
+    <row r="1642" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1642" t="s">
+        <v>5874</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>5875</v>
+      </c>
+      <c r="C1642" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1642" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1642" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1642" t="s">
+        <v>5876</v>
+      </c>
+      <c r="G1642" s="1">
+        <v>46844</v>
+      </c>
+      <c r="H1642">
+        <v>2012</v>
+      </c>
+      <c r="I1642" s="4" t="s">
+        <v>5877</v>
+      </c>
+      <c r="J1642" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1642" s="4" t="s">
+        <v>4033</v>
+      </c>
+      <c r="L1642" s="4" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1643" t="s">
+        <v>5878</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>5879</v>
+      </c>
+      <c r="C1643" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1643" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1643" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1643" t="s">
+        <v>5880</v>
+      </c>
+      <c r="G1643" s="1">
+        <v>46722</v>
+      </c>
+      <c r="H1643">
+        <v>984</v>
+      </c>
+      <c r="I1643" s="4" t="s">
+        <v>5881</v>
+      </c>
+      <c r="J1643" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1643" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1643" s="4" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1644" t="s">
+        <v>5882</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>5883</v>
+      </c>
+      <c r="C1644" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1644" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1644" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1644" t="s">
+        <v>5884</v>
+      </c>
+      <c r="G1644" s="1">
+        <v>46753</v>
+      </c>
+      <c r="H1644">
+        <v>3595</v>
+      </c>
+      <c r="I1644" s="4" t="s">
+        <v>5885</v>
+      </c>
+      <c r="J1644" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1644" s="4" t="s">
+        <v>4271</v>
+      </c>
+      <c r="L1644" s="4" t="s">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1645" t="s">
+        <v>5886</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>5887</v>
+      </c>
+      <c r="C1645" s="4" t="s">
+        <v>3890</v>
+      </c>
+      <c r="D1645" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1645" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1645" t="s">
+        <v>5888</v>
+      </c>
+      <c r="G1645" s="1">
+        <v>46692</v>
+      </c>
+      <c r="H1645">
+        <v>29</v>
+      </c>
+      <c r="I1645" s="4" t="s">
+        <v>5889</v>
+      </c>
+      <c r="J1645" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1645" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1645" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1646" t="s">
+        <v>5890</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>5891</v>
+      </c>
+      <c r="C1646" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1646" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1646" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1646" t="s">
+        <v>5892</v>
+      </c>
+      <c r="G1646" s="1">
+        <v>46722</v>
+      </c>
+      <c r="H1646">
+        <v>5832</v>
+      </c>
+      <c r="I1646" s="4" t="s">
+        <v>5893</v>
+      </c>
+      <c r="J1646" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1646" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1646" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1647" t="s">
+        <v>5894</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>5895</v>
+      </c>
+      <c r="C1647" s="4" t="s">
+        <v>3864</v>
+      </c>
+      <c r="D1647" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1647" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1647" t="s">
+        <v>5896</v>
+      </c>
+      <c r="G1647" s="1">
+        <v>46874</v>
+      </c>
+      <c r="H1647">
+        <v>103</v>
+      </c>
+      <c r="I1647" s="4" t="s">
+        <v>5897</v>
+      </c>
+      <c r="J1647" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1647" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1647" s="4" t="s">
+        <v>4252</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1648" t="s">
+        <v>5898</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>5899</v>
+      </c>
+      <c r="C1648" s="4" t="s">
+        <v>3886</v>
+      </c>
+      <c r="D1648" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1648" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1648" t="s">
+        <v>5772</v>
+      </c>
+      <c r="G1648" s="1">
+        <v>46023</v>
+      </c>
+      <c r="H1648">
+        <v>8</v>
+      </c>
+      <c r="I1648" s="4" t="s">
+        <v>5900</v>
+      </c>
+      <c r="J1648" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1648" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1648" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1649" t="s">
+        <v>5901</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>5902</v>
+      </c>
+      <c r="C1649" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1649" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1649" t="s">
+        <v>5903</v>
+      </c>
+      <c r="G1649" s="1">
+        <v>46631</v>
+      </c>
+      <c r="H1649">
+        <v>580</v>
+      </c>
+      <c r="I1649" s="4" t="s">
+        <v>5904</v>
+      </c>
+      <c r="J1649" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1649" s="4" t="s">
+        <v>4208</v>
+      </c>
+      <c r="L1649" s="4" t="s">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1650" t="s">
+        <v>5906</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>5907</v>
+      </c>
+      <c r="C1650" s="4" t="s">
+        <v>3944</v>
+      </c>
+      <c r="D1650" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1650" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1650" t="s">
+        <v>5908</v>
+      </c>
+      <c r="G1650" s="1">
+        <v>46600</v>
+      </c>
+      <c r="H1650">
+        <v>2456</v>
+      </c>
+      <c r="I1650" s="4" t="s">
+        <v>5909</v>
+      </c>
+      <c r="J1650" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1650" s="4" t="s">
+        <v>4271</v>
+      </c>
+      <c r="L1650" s="4" t="s">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1651" t="s">
+        <v>5910</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>5911</v>
+      </c>
+      <c r="C1651" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1651" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1651" t="s">
+        <v>5912</v>
+      </c>
+      <c r="G1651" s="1">
+        <v>46874</v>
+      </c>
+      <c r="H1651">
+        <v>0</v>
+      </c>
+      <c r="I1651" s="4" t="s">
+        <v>5913</v>
+      </c>
+      <c r="J1651" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1651" s="4" t="s">
+        <v>4175</v>
+      </c>
+      <c r="L1651" s="4" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1652" t="s">
+        <v>5914</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>5915</v>
+      </c>
+      <c r="C1652" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1652" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1652" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1652" t="s">
+        <v>5916</v>
+      </c>
+      <c r="G1652" s="1">
+        <v>46631</v>
+      </c>
+      <c r="H1652">
+        <v>1505</v>
+      </c>
+      <c r="I1652" s="4" t="s">
+        <v>5917</v>
+      </c>
+      <c r="J1652" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1652" s="4" t="s">
+        <v>5857</v>
+      </c>
+      <c r="L1652" s="4" t="s">
+        <v>5794</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1653" t="s">
+        <v>5918</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>5919</v>
+      </c>
+      <c r="C1653" s="4" t="s">
+        <v>5920</v>
+      </c>
+      <c r="D1653" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1653" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1653" t="s">
+        <v>5921</v>
+      </c>
+      <c r="G1653" s="1">
+        <v>46388</v>
+      </c>
+      <c r="H1653">
+        <v>5672</v>
+      </c>
+      <c r="I1653" s="4" t="s">
+        <v>5922</v>
+      </c>
+      <c r="J1653" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1653" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1653" s="4" t="s">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1654" t="s">
+        <v>5923</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>5924</v>
+      </c>
+      <c r="C1654" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1654" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1654" t="s">
+        <v>5925</v>
+      </c>
+      <c r="G1654" s="1">
+        <v>46631</v>
+      </c>
+      <c r="H1654">
+        <v>12</v>
+      </c>
+      <c r="I1654" s="4" t="s">
+        <v>5926</v>
+      </c>
+      <c r="J1654" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1654" s="4" t="s">
+        <v>4266</v>
+      </c>
+      <c r="L1654" s="4"/>
+    </row>
+    <row r="1655" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1655" t="s">
+        <v>5927</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>5928</v>
+      </c>
+      <c r="C1655" s="4" t="s">
+        <v>3864</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1655" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1655" t="s">
+        <v>5929</v>
+      </c>
+      <c r="G1655" s="1">
+        <v>46874</v>
+      </c>
+      <c r="H1655">
+        <v>986</v>
+      </c>
+      <c r="I1655" s="4" t="s">
+        <v>5930</v>
+      </c>
+      <c r="J1655" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1655" s="4" t="s">
+        <v>4208</v>
+      </c>
+      <c r="L1655" s="4" t="s">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1656" t="s">
+        <v>5931</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>5932</v>
+      </c>
+      <c r="C1656" s="4" t="s">
+        <v>3890</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1656" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1656" t="s">
+        <v>5933</v>
+      </c>
+      <c r="G1656" s="1">
+        <v>46692</v>
+      </c>
+      <c r="H1656">
+        <v>2219</v>
+      </c>
+      <c r="I1656" s="4" t="s">
+        <v>5934</v>
+      </c>
+      <c r="J1656" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1656" s="4"/>
+      <c r="L1656" s="4" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1657" t="s">
+        <v>5935</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>5936</v>
+      </c>
+      <c r="C1657" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1657" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1657" t="s">
+        <v>5937</v>
+      </c>
+      <c r="G1657" s="1">
+        <v>46447</v>
+      </c>
+      <c r="H1657">
+        <v>5402</v>
+      </c>
+      <c r="I1657" s="4" t="s">
+        <v>5938</v>
+      </c>
+      <c r="J1657" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1657" s="4"/>
+      <c r="L1657" s="4" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1658" t="s">
+        <v>5939</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>5940</v>
+      </c>
+      <c r="C1658" s="4" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1658" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1658" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1658" t="s">
+        <v>5941</v>
+      </c>
+      <c r="G1658" s="1">
+        <v>46661</v>
+      </c>
+      <c r="H1658">
+        <v>875</v>
+      </c>
+      <c r="I1658" s="4" t="s">
+        <v>5942</v>
+      </c>
+      <c r="J1658" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1658" s="4"/>
+      <c r="L1658" s="4" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1659" t="s">
+        <v>5943</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>5944</v>
+      </c>
+      <c r="C1659" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1659" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1659" t="s">
+        <v>5945</v>
+      </c>
+      <c r="G1659" s="1">
+        <v>46905</v>
+      </c>
+      <c r="H1659">
+        <v>3325</v>
+      </c>
+      <c r="I1659" s="4" t="s">
+        <v>5946</v>
+      </c>
+      <c r="J1659" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1659" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1659" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1660" t="s">
+        <v>5947</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>5948</v>
+      </c>
+      <c r="C1660" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1660" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1660" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1660" t="s">
+        <v>5949</v>
+      </c>
+      <c r="G1660" s="1">
+        <v>46631</v>
+      </c>
+      <c r="H1660">
+        <v>1773</v>
+      </c>
+      <c r="I1660" s="4" t="s">
+        <v>5950</v>
+      </c>
+      <c r="J1660" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1660" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1660" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1661" t="s">
+        <v>5951</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>5952</v>
+      </c>
+      <c r="C1661" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1661" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1661" t="s">
+        <v>5953</v>
+      </c>
+      <c r="G1661" s="1">
+        <v>46631</v>
+      </c>
+      <c r="H1661">
+        <v>315</v>
+      </c>
+      <c r="I1661" s="4" t="s">
+        <v>5954</v>
+      </c>
+      <c r="J1661" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1661" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1661" s="4" t="s">
+        <v>4252</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1662" t="s">
+        <v>5955</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>5956</v>
+      </c>
+      <c r="C1662" s="4" t="s">
+        <v>3890</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1662" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1662" t="s">
+        <v>5957</v>
+      </c>
+      <c r="G1662" s="1">
+        <v>46722</v>
+      </c>
+      <c r="H1662">
+        <v>3507</v>
+      </c>
+      <c r="I1662" s="4" t="s">
+        <v>5958</v>
+      </c>
+      <c r="J1662" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1662" s="4"/>
+      <c r="L1662" s="4" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1663" t="s">
+        <v>5959</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>5960</v>
+      </c>
+      <c r="C1663" s="4" t="s">
+        <v>3864</v>
+      </c>
+      <c r="D1663" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1663" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1663" t="s">
+        <v>5961</v>
+      </c>
+      <c r="G1663" s="1">
+        <v>46692</v>
+      </c>
+      <c r="H1663">
+        <v>131</v>
+      </c>
+      <c r="I1663" s="4" t="s">
+        <v>5962</v>
+      </c>
+      <c r="J1663" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1663" s="4" t="s">
+        <v>4208</v>
+      </c>
+      <c r="L1663" s="4" t="s">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1664" t="s">
+        <v>5963</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>5964</v>
+      </c>
+      <c r="C1664" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1664" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1664" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1664" t="s">
+        <v>5965</v>
+      </c>
+      <c r="G1664" s="1">
+        <v>47027</v>
+      </c>
+      <c r="H1664">
+        <v>79</v>
+      </c>
+      <c r="I1664" s="4" t="s">
+        <v>5966</v>
+      </c>
+      <c r="J1664" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1664" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1664" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1665" t="s">
+        <v>5967</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>5968</v>
+      </c>
+      <c r="C1665" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1665" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1665" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1665" t="s">
+        <v>5969</v>
+      </c>
+      <c r="G1665" s="1">
+        <v>47027</v>
+      </c>
+      <c r="H1665">
+        <v>410</v>
+      </c>
+      <c r="I1665" s="4" t="s">
+        <v>5970</v>
+      </c>
+      <c r="J1665" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1665" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1665" s="4" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1666" t="s">
+        <v>5971</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>5972</v>
+      </c>
+      <c r="C1666" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1666" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1666" t="s">
+        <v>5973</v>
+      </c>
+      <c r="G1666" s="1">
+        <v>47239</v>
+      </c>
+      <c r="H1666">
+        <v>790</v>
+      </c>
+      <c r="I1666" s="4" t="s">
+        <v>5974</v>
+      </c>
+      <c r="J1666" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1666" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1666" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1667" t="s">
+        <v>5975</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>5976</v>
+      </c>
+      <c r="C1667" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1667" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1667" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1667" t="s">
+        <v>5977</v>
+      </c>
+      <c r="G1667" s="1">
+        <v>47239</v>
+      </c>
+      <c r="H1667">
+        <v>950</v>
+      </c>
+      <c r="I1667" s="4" t="s">
+        <v>5978</v>
+      </c>
+      <c r="J1667" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1667" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1667" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1668" t="s">
+        <v>5979</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>5980</v>
+      </c>
+      <c r="C1668" s="4" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1668" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1668" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1668" t="s">
+        <v>5981</v>
+      </c>
+      <c r="G1668" s="1">
+        <v>46631</v>
+      </c>
+      <c r="H1668">
+        <v>106</v>
+      </c>
+      <c r="I1668" s="4" t="s">
+        <v>5982</v>
+      </c>
+      <c r="J1668" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1668" s="4" t="s">
+        <v>4266</v>
+      </c>
+      <c r="L1668" s="4" t="s">
+        <v>5983</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1669" t="s">
+        <v>5984</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>5985</v>
+      </c>
+      <c r="C1669" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1669" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1669" t="s">
+        <v>5986</v>
+      </c>
+      <c r="G1669" s="1">
+        <v>47058</v>
+      </c>
+      <c r="H1669">
+        <v>431</v>
+      </c>
+      <c r="I1669" s="4" t="s">
+        <v>5987</v>
+      </c>
+      <c r="J1669" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1669" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1669" s="4" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1670" t="s">
+        <v>5988</v>
+      </c>
+      <c r="C1670" s="4" t="s">
+        <v>3858</v>
+      </c>
+      <c r="D1670" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1670" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1670" t="s">
+        <v>5989</v>
+      </c>
+      <c r="G1670" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1670">
+        <v>0</v>
+      </c>
+      <c r="I1670" s="4" t="s">
+        <v>5990</v>
+      </c>
+      <c r="J1670" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1670" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1670" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1671" t="s">
+        <v>5991</v>
+      </c>
+      <c r="C1671" s="4" t="s">
+        <v>3930</v>
+      </c>
+      <c r="D1671" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1671" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1671" t="s">
+        <v>4101</v>
+      </c>
+      <c r="G1671" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1671">
+        <v>0</v>
+      </c>
+      <c r="I1671" s="4" t="s">
+        <v>5992</v>
+      </c>
+      <c r="J1671" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1671" s="4" t="s">
+        <v>4100</v>
+      </c>
+      <c r="L1671" s="4" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1672" t="s">
+        <v>5993</v>
+      </c>
+      <c r="C1672" s="4" t="s">
+        <v>3903</v>
+      </c>
+      <c r="D1672" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1672" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1672" t="s">
+        <v>5994</v>
+      </c>
+      <c r="G1672" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1672">
+        <v>0</v>
+      </c>
+      <c r="I1672" s="4" t="s">
+        <v>5995</v>
+      </c>
+      <c r="J1672" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1672" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1672" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1673" t="s">
+        <v>5996</v>
+      </c>
+      <c r="C1673" s="4" t="s">
+        <v>3910</v>
+      </c>
+      <c r="D1673" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1673" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1673" t="s">
+        <v>5828</v>
+      </c>
+      <c r="G1673" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1673">
+        <v>0</v>
+      </c>
+      <c r="I1673" s="4" t="s">
+        <v>5997</v>
+      </c>
+      <c r="J1673" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1673" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1673" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1674" t="s">
+        <v>5998</v>
+      </c>
+      <c r="C1674" s="4" t="s">
+        <v>3913</v>
+      </c>
+      <c r="D1674" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1674" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1674" t="s">
+        <v>5999</v>
+      </c>
+      <c r="G1674" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1674">
+        <v>0</v>
+      </c>
+      <c r="I1674" s="4" t="s">
+        <v>6000</v>
+      </c>
+      <c r="J1674" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1674" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1674" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1675" t="s">
+        <v>6001</v>
+      </c>
+      <c r="C1675" s="4" t="s">
+        <v>3901</v>
+      </c>
+      <c r="D1675" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1675" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1675" t="s">
+        <v>6002</v>
+      </c>
+      <c r="G1675" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1675">
+        <v>0</v>
+      </c>
+      <c r="I1675" s="4" t="s">
+        <v>6003</v>
+      </c>
+      <c r="J1675" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1675" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1675" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1676" t="s">
+        <v>6004</v>
+      </c>
+      <c r="C1676" s="4" t="s">
+        <v>3908</v>
+      </c>
+      <c r="D1676" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1676" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1676" t="s">
+        <v>6005</v>
+      </c>
+      <c r="G1676" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1676">
+        <v>0</v>
+      </c>
+      <c r="I1676" s="4" t="s">
+        <v>6006</v>
+      </c>
+      <c r="J1676" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1676" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1676" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1677" t="s">
+        <v>6007</v>
+      </c>
+      <c r="C1677" s="4" t="s">
+        <v>3853</v>
+      </c>
+      <c r="D1677" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1677" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1677" t="s">
+        <v>6008</v>
+      </c>
+      <c r="G1677" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1677">
+        <v>0</v>
+      </c>
+      <c r="I1677" s="4" t="s">
+        <v>6009</v>
+      </c>
+      <c r="J1677" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1677" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1677" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1678" t="s">
+        <v>6010</v>
+      </c>
+      <c r="C1678" s="4" t="s">
+        <v>3908</v>
+      </c>
+      <c r="D1678" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1678" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1678" t="s">
+        <v>6011</v>
+      </c>
+      <c r="G1678" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1678">
+        <v>0</v>
+      </c>
+      <c r="I1678" s="4" t="s">
+        <v>6012</v>
+      </c>
+      <c r="J1678" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1678" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1678" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1679" t="s">
+        <v>6013</v>
+      </c>
+      <c r="C1679" s="4" t="s">
+        <v>3847</v>
+      </c>
+      <c r="D1679" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1679" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1679" t="s">
+        <v>6014</v>
+      </c>
+      <c r="G1679" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1679">
+        <v>0</v>
+      </c>
+      <c r="I1679" s="4" t="s">
+        <v>6015</v>
+      </c>
+      <c r="J1679" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1679" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1679" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1680" t="s">
+        <v>6016</v>
+      </c>
+      <c r="C1680" s="4" t="s">
+        <v>3847</v>
+      </c>
+      <c r="D1680" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1680" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1680" t="s">
+        <v>5860</v>
+      </c>
+      <c r="G1680" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1680">
+        <v>0</v>
+      </c>
+      <c r="I1680" s="4" t="s">
+        <v>6017</v>
+      </c>
+      <c r="J1680" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1680" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1680" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1681" t="s">
+        <v>6018</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>6019</v>
+      </c>
+      <c r="C1681" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1681" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1681" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1681" t="s">
+        <v>5994</v>
+      </c>
+      <c r="G1681" s="1">
+        <v>46447</v>
+      </c>
+      <c r="H1681">
+        <v>1030</v>
+      </c>
+      <c r="I1681" s="4" t="s">
+        <v>6020</v>
+      </c>
+      <c r="J1681" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1681" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1681" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1682" t="s">
+        <v>6021</v>
+      </c>
+      <c r="C1682" s="4" t="s">
+        <v>3908</v>
+      </c>
+      <c r="D1682" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1682" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1682" t="s">
+        <v>6022</v>
+      </c>
+      <c r="G1682" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1682">
+        <v>0</v>
+      </c>
+      <c r="I1682" s="4" t="s">
+        <v>6023</v>
+      </c>
+      <c r="J1682" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1682" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1682" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1683" t="s">
+        <v>6024</v>
+      </c>
+      <c r="C1683" s="4" t="s">
+        <v>3911</v>
+      </c>
+      <c r="D1683" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1683" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1683" t="s">
+        <v>6025</v>
+      </c>
+      <c r="G1683" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1683">
+        <v>0</v>
+      </c>
+      <c r="I1683" s="4" t="s">
+        <v>6026</v>
+      </c>
+      <c r="J1683" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1683" s="4" t="s">
+        <v>4032</v>
+      </c>
+      <c r="L1683" s="4" t="s">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1684" t="s">
+        <v>6027</v>
+      </c>
+      <c r="C1684" s="4" t="s">
+        <v>3876</v>
+      </c>
+      <c r="D1684" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1684" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1684" t="s">
+        <v>6028</v>
+      </c>
+      <c r="G1684" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1684">
+        <v>0</v>
+      </c>
+      <c r="I1684" s="4" t="s">
+        <v>6029</v>
+      </c>
+      <c r="J1684" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1684" s="4" t="s">
+        <v>4266</v>
+      </c>
+      <c r="L1684" s="4" t="s">
+        <v>5794</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1685" t="s">
+        <v>6030</v>
+      </c>
+      <c r="C1685" s="4" t="s">
+        <v>3925</v>
+      </c>
+      <c r="D1685" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1685" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1685" t="s">
+        <v>6031</v>
+      </c>
+      <c r="G1685" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1685">
+        <v>232</v>
+      </c>
+      <c r="I1685" s="4" t="s">
+        <v>6032</v>
+      </c>
+      <c r="J1685" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1685" s="4" t="s">
+        <v>5857</v>
+      </c>
+      <c r="L1685" s="4" t="s">
+        <v>5794</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1686" t="s">
+        <v>6033</v>
+      </c>
+      <c r="C1686" s="4" t="s">
+        <v>3903</v>
+      </c>
+      <c r="D1686" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1686" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1686" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1686">
+        <v>0</v>
+      </c>
+      <c r="I1686" s="4" t="s">
+        <v>6034</v>
+      </c>
+      <c r="J1686" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1686" s="4" t="s">
+        <v>4266</v>
+      </c>
+      <c r="L1686" s="4" t="s">
+        <v>5983</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1687" t="s">
+        <v>6035</v>
+      </c>
+      <c r="C1687" s="4" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D1687" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1687" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1687" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1687" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1687">
+        <v>0</v>
+      </c>
+      <c r="I1687" s="4" t="s">
+        <v>6036</v>
+      </c>
+      <c r="J1687" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1687" s="4"/>
+      <c r="L1687" s="4"/>
+    </row>
+    <row r="1688" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1688" t="s">
+        <v>6037</v>
+      </c>
+      <c r="C1688" s="4" t="s">
+        <v>3895</v>
+      </c>
+      <c r="D1688" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1688" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1688" t="s">
+        <v>6038</v>
+      </c>
+      <c r="G1688" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1688">
+        <v>0</v>
+      </c>
+      <c r="I1688" s="4" t="s">
+        <v>6039</v>
+      </c>
+      <c r="J1688" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1688" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1688" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1689" t="s">
+        <v>6040</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>6041</v>
+      </c>
+      <c r="C1689" s="4" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1689" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1689" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1689" t="s">
+        <v>6042</v>
+      </c>
+      <c r="G1689" s="1">
+        <v>46874</v>
+      </c>
+      <c r="H1689">
+        <v>2127</v>
+      </c>
+      <c r="I1689" s="4" t="s">
+        <v>6043</v>
+      </c>
+      <c r="J1689" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1689" s="4"/>
+      <c r="L1689" s="4"/>
+    </row>
+    <row r="1690" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1690" t="s">
+        <v>6044</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>6045</v>
+      </c>
+      <c r="C1690" s="4" t="s">
+        <v>3878</v>
+      </c>
+      <c r="D1690" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1690" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1690" t="s">
+        <v>6046</v>
+      </c>
+      <c r="G1690" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H1690">
+        <v>6462</v>
+      </c>
+      <c r="I1690" s="4" t="s">
+        <v>6047</v>
+      </c>
+      <c r="J1690" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1690" s="4"/>
+      <c r="L1690" s="4"/>
+    </row>
+    <row r="1691" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1691" t="s">
+        <v>6048</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>6049</v>
+      </c>
+      <c r="C1691" s="4" t="s">
+        <v>3865</v>
+      </c>
+      <c r="D1691" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1691" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1691" t="s">
+        <v>6050</v>
+      </c>
+      <c r="G1691" s="1">
+        <v>46174</v>
+      </c>
+      <c r="H1691">
+        <v>1490</v>
+      </c>
+      <c r="I1691" s="4" t="s">
+        <v>6051</v>
+      </c>
+      <c r="J1691" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1691" s="4" t="s">
+        <v>4010</v>
+      </c>
+      <c r="L1691" s="4" t="s">
+        <v>6052</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1692" t="s">
+        <v>6053</v>
+      </c>
+      <c r="C1692" s="4" t="s">
+        <v>6054</v>
+      </c>
+      <c r="D1692" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1692" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1692" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1692" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1692">
+        <v>0</v>
+      </c>
+      <c r="I1692" s="4" t="s">
+        <v>6055</v>
+      </c>
+      <c r="J1692" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1692" s="4" t="s">
+        <v>4033</v>
+      </c>
+      <c r="L1692" s="4" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1693" t="s">
+        <v>6056</v>
+      </c>
+      <c r="C1693" s="4" t="s">
+        <v>6054</v>
+      </c>
+      <c r="D1693" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1693" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1693" t="s">
+        <v>6057</v>
+      </c>
+      <c r="G1693" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1693">
+        <v>0</v>
+      </c>
+      <c r="I1693" s="4" t="s">
+        <v>6058</v>
+      </c>
+      <c r="J1693" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1693" s="4" t="s">
+        <v>4033</v>
+      </c>
+      <c r="L1693" s="4" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1694" t="s">
+        <v>6059</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>6060</v>
+      </c>
+      <c r="C1694" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1694" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1694" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1694" t="s">
+        <v>6061</v>
+      </c>
+      <c r="G1694" s="1">
+        <v>46753</v>
+      </c>
+      <c r="H1694">
+        <v>1055</v>
+      </c>
+      <c r="I1694" s="4" t="s">
+        <v>6062</v>
+      </c>
+      <c r="J1694" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1694" s="4" t="s">
+        <v>4266</v>
+      </c>
+      <c r="L1694" s="4" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1695" t="s">
+        <v>6063</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>6064</v>
+      </c>
+      <c r="C1695" s="4" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1695" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1695" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1695" t="s">
+        <v>6065</v>
+      </c>
+      <c r="G1695" s="1">
+        <v>46661</v>
+      </c>
+      <c r="H1695">
+        <v>287</v>
+      </c>
+      <c r="I1695" s="4" t="s">
+        <v>6066</v>
+      </c>
+      <c r="J1695" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1695" s="4" t="s">
+        <v>4108</v>
+      </c>
+      <c r="L1695" s="4" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1696" t="s">
+        <v>6067</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>6068</v>
+      </c>
+      <c r="C1696" s="4" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1696" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1696" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1696" t="s">
+        <v>6069</v>
+      </c>
+      <c r="G1696" s="1">
+        <v>46661</v>
+      </c>
+      <c r="H1696">
+        <v>586</v>
+      </c>
+      <c r="I1696" s="4" t="s">
+        <v>6070</v>
+      </c>
+      <c r="J1696" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1696" s="4" t="s">
+        <v>4108</v>
+      </c>
+      <c r="L1696" s="4" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1697" t="s">
+        <v>6071</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>6072</v>
+      </c>
+      <c r="C1697" s="4" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1697" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1697" t="s">
+        <v>6073</v>
+      </c>
+      <c r="G1697" s="1">
+        <v>46692</v>
+      </c>
+      <c r="H1697">
+        <v>999</v>
+      </c>
+      <c r="I1697" s="4" t="s">
+        <v>6074</v>
+      </c>
+      <c r="J1697" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1697" s="4" t="s">
+        <v>4108</v>
+      </c>
+      <c r="L1697" s="4" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1698" t="s">
+        <v>6075</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>6076</v>
+      </c>
+      <c r="C1698" s="4" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1698" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1698" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1698" t="s">
+        <v>6077</v>
+      </c>
+      <c r="G1698" s="1">
+        <v>46784</v>
+      </c>
+      <c r="H1698">
+        <v>938</v>
+      </c>
+      <c r="I1698" s="4" t="s">
+        <v>6078</v>
+      </c>
+      <c r="J1698" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1698" s="4" t="s">
+        <v>4108</v>
+      </c>
+      <c r="L1698" s="4" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1699" t="s">
+        <v>6079</v>
+      </c>
+      <c r="C1699" s="4" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1699" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1699" t="s">
+        <v>6080</v>
+      </c>
+      <c r="G1699" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1699">
+        <v>0</v>
+      </c>
+      <c r="I1699" s="4" t="s">
+        <v>6081</v>
+      </c>
+      <c r="J1699" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1699" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1699" s="4" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1700" t="s">
+        <v>6083</v>
+      </c>
+      <c r="C1700" s="4" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D1700" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1700" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1700" t="s">
+        <v>6084</v>
+      </c>
+      <c r="G1700" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1700">
+        <v>0</v>
+      </c>
+      <c r="I1700" s="4" t="s">
+        <v>6085</v>
+      </c>
+      <c r="J1700" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1700" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1700" s="4" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1701" t="s">
+        <v>6086</v>
+      </c>
+      <c r="C1701" s="4" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1701" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1701" t="s">
+        <v>6087</v>
+      </c>
+      <c r="G1701" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1701">
+        <v>0</v>
+      </c>
+      <c r="I1701" s="4" t="s">
+        <v>6088</v>
+      </c>
+      <c r="J1701" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1701" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1701" s="4" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1702" t="s">
+        <v>6089</v>
+      </c>
+      <c r="C1702" s="4" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D1702" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1702" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1702" t="s">
+        <v>6090</v>
+      </c>
+      <c r="G1702" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1702">
+        <v>0</v>
+      </c>
+      <c r="I1702" s="4" t="s">
+        <v>6091</v>
+      </c>
+      <c r="J1702" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1702" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1702" s="4" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1703" t="s">
+        <v>6092</v>
+      </c>
+      <c r="C1703" s="4" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1703" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1703" t="s">
+        <v>6093</v>
+      </c>
+      <c r="G1703" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1703">
+        <v>0</v>
+      </c>
+      <c r="I1703" s="4" t="s">
+        <v>6094</v>
+      </c>
+      <c r="J1703" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1703" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1703" s="4" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1704" t="s">
+        <v>6095</v>
+      </c>
+      <c r="C1704" s="4" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D1704" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1704" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1704" t="s">
+        <v>6096</v>
+      </c>
+      <c r="G1704" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1704">
+        <v>0</v>
+      </c>
+      <c r="I1704" s="4" t="s">
+        <v>6097</v>
+      </c>
+      <c r="J1704" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1704" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1704" s="4" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1705" t="s">
+        <v>6098</v>
+      </c>
+      <c r="C1705" s="4" t="s">
+        <v>3848</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1705" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1705" t="s">
+        <v>6099</v>
+      </c>
+      <c r="G1705" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1705">
+        <v>0</v>
+      </c>
+      <c r="I1705" s="4" t="s">
+        <v>6100</v>
+      </c>
+      <c r="J1705" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1705" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1705" s="4" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1706" t="s">
+        <v>6101</v>
+      </c>
+      <c r="C1706" s="4" t="s">
+        <v>3894</v>
+      </c>
+      <c r="D1706" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1706" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1706" t="s">
+        <v>6102</v>
+      </c>
+      <c r="G1706" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1706">
+        <v>0</v>
+      </c>
+      <c r="I1706" s="4" t="s">
+        <v>6103</v>
+      </c>
+      <c r="J1706" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1706" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1706" s="4" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1707" t="s">
+        <v>6104</v>
+      </c>
+      <c r="C1707" s="4" t="s">
+        <v>3906</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1707" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1707" t="s">
+        <v>638</v>
+      </c>
+      <c r="G1707" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1707">
+        <v>105</v>
+      </c>
+      <c r="I1707" s="4" t="s">
+        <v>6105</v>
+      </c>
+      <c r="J1707" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1707" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1707" s="4" t="s">
+        <v>6052</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1708" t="s">
+        <v>6106</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>6107</v>
+      </c>
+      <c r="C1708" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1708" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1708" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1708" t="s">
+        <v>6108</v>
+      </c>
+      <c r="G1708" s="1">
+        <v>46844</v>
+      </c>
+      <c r="H1708">
+        <v>2478</v>
+      </c>
+      <c r="I1708" s="4" t="s">
+        <v>6109</v>
+      </c>
+      <c r="J1708" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1708" s="4" t="s">
+        <v>4032</v>
+      </c>
+      <c r="L1708" s="4"/>
+    </row>
+    <row r="1709" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1709" t="s">
+        <v>6110</v>
+      </c>
+      <c r="C1709" s="4" t="s">
+        <v>3937</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1709" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1709" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G1709" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1709">
+        <v>0</v>
+      </c>
+      <c r="I1709" s="4" t="s">
+        <v>6111</v>
+      </c>
+      <c r="J1709" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1709" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1709" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1710" t="s">
+        <v>6112</v>
+      </c>
+      <c r="C1710" s="4" t="s">
+        <v>3883</v>
+      </c>
+      <c r="D1710" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1710" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1710" t="s">
+        <v>229</v>
+      </c>
+      <c r="G1710" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1710">
+        <v>0</v>
+      </c>
+      <c r="I1710" s="4" t="s">
+        <v>6113</v>
+      </c>
+      <c r="J1710" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1710" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1710" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1711" t="s">
+        <v>6114</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>6115</v>
+      </c>
+      <c r="C1711" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1711" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1711" t="s">
+        <v>6116</v>
+      </c>
+      <c r="G1711" s="1">
+        <v>46631</v>
+      </c>
+      <c r="H1711">
+        <v>2170</v>
+      </c>
+      <c r="I1711" s="4" t="s">
+        <v>6117</v>
+      </c>
+      <c r="J1711" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1711" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1711" s="4" t="s">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1712" t="s">
+        <v>6118</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>6119</v>
+      </c>
+      <c r="C1712" s="4" t="s">
+        <v>3877</v>
+      </c>
+      <c r="D1712" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1712" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1712" t="s">
+        <v>592</v>
+      </c>
+      <c r="G1712" s="1">
+        <v>47300</v>
+      </c>
+      <c r="H1712">
+        <v>1470</v>
+      </c>
+      <c r="I1712" s="4" t="s">
+        <v>6120</v>
+      </c>
+      <c r="J1712" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1712" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1712" s="4" t="s">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1713" t="s">
+        <v>6121</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>6122</v>
+      </c>
+      <c r="C1713" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1713" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1713" t="s">
+        <v>6123</v>
+      </c>
+      <c r="G1713" s="1">
+        <v>46722</v>
+      </c>
+      <c r="H1713">
+        <v>9582</v>
+      </c>
+      <c r="I1713" s="4" t="s">
+        <v>6124</v>
+      </c>
+      <c r="J1713" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1713" s="4" t="s">
+        <v>4208</v>
+      </c>
+      <c r="L1713" s="4" t="s">
+        <v>5905</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1714" t="s">
+        <v>6125</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>6126</v>
+      </c>
+      <c r="C1714" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1714" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1714" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1714" t="s">
+        <v>6116</v>
+      </c>
+      <c r="G1714" s="1">
+        <v>46784</v>
+      </c>
+      <c r="H1714">
+        <v>1518</v>
+      </c>
+      <c r="I1714" s="4" t="s">
+        <v>6127</v>
+      </c>
+      <c r="J1714" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1714" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1714" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1715" t="s">
+        <v>6128</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>6129</v>
+      </c>
+      <c r="C1715" s="4" t="s">
+        <v>3868</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1715" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1715" t="s">
+        <v>6130</v>
+      </c>
+      <c r="G1715" s="1">
+        <v>46631</v>
+      </c>
+      <c r="H1715">
+        <v>263</v>
+      </c>
+      <c r="I1715" s="4" t="s">
+        <v>6131</v>
+      </c>
+      <c r="J1715" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1715" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1715" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1716" t="s">
+        <v>6132</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>6133</v>
+      </c>
+      <c r="C1716" s="4" t="s">
+        <v>3845</v>
+      </c>
+      <c r="D1716" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1716" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1716" t="s">
+        <v>6031</v>
+      </c>
+      <c r="G1716" s="1">
+        <v>46692</v>
+      </c>
+      <c r="H1716">
+        <v>2437</v>
+      </c>
+      <c r="I1716" s="4" t="s">
+        <v>6134</v>
+      </c>
+      <c r="J1716" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1716" s="4" t="s">
+        <v>4108</v>
+      </c>
+      <c r="L1716" s="4" t="s">
+        <v>5794</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1717" t="s">
+        <v>6135</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>6136</v>
+      </c>
+      <c r="C1717" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1717" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1717" t="s">
+        <v>6137</v>
+      </c>
+      <c r="G1717" s="1">
+        <v>46722</v>
+      </c>
+      <c r="H1717">
+        <v>10923</v>
+      </c>
+      <c r="I1717" s="4" t="s">
+        <v>6138</v>
+      </c>
+      <c r="J1717" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1717" s="4"/>
+      <c r="L1717" s="4"/>
+    </row>
+    <row r="1718" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1718" t="s">
+        <v>6139</v>
+      </c>
+      <c r="C1718" s="4" t="s">
+        <v>3891</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1718" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1718" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1718" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1718">
+        <v>301</v>
+      </c>
+      <c r="I1718" s="4" t="s">
+        <v>6140</v>
+      </c>
+      <c r="J1718" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1718" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1718" s="4" t="s">
+        <v>6052</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1719" t="s">
+        <v>6141</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>6142</v>
+      </c>
+      <c r="C1719" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1719" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1719" t="s">
+        <v>6143</v>
+      </c>
+      <c r="G1719" s="1">
+        <v>46722</v>
+      </c>
+      <c r="H1719">
+        <v>2366</v>
+      </c>
+      <c r="I1719" s="4" t="s">
+        <v>6144</v>
+      </c>
+      <c r="J1719" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1719" s="4" t="s">
+        <v>4258</v>
+      </c>
+      <c r="L1719" s="4" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1720" t="s">
+        <v>6145</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>6146</v>
+      </c>
+      <c r="C1720" s="4" t="s">
+        <v>3864</v>
+      </c>
+      <c r="D1720" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1720" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1720" t="s">
+        <v>6147</v>
+      </c>
+      <c r="G1720" s="1">
+        <v>46997</v>
+      </c>
+      <c r="H1720">
+        <v>1536</v>
+      </c>
+      <c r="I1720" s="4" t="s">
+        <v>6148</v>
+      </c>
+      <c r="J1720" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1720" s="4" t="s">
+        <v>4100</v>
+      </c>
+      <c r="L1720" s="4" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1721" t="s">
+        <v>6149</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>6150</v>
+      </c>
+      <c r="C1721" s="4" t="s">
+        <v>3849</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1721" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1721" t="s">
+        <v>909</v>
+      </c>
+      <c r="G1721" s="1">
+        <v>46661</v>
+      </c>
+      <c r="H1721">
+        <v>428</v>
+      </c>
+      <c r="I1721" s="4" t="s">
+        <v>6151</v>
+      </c>
+      <c r="J1721" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1721" s="4" t="s">
+        <v>4105</v>
+      </c>
+      <c r="L1721" s="4" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1722" t="s">
+        <v>6152</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>6153</v>
+      </c>
+      <c r="C1722" s="4" t="s">
+        <v>3885</v>
+      </c>
+      <c r="D1722" t="s">
+        <v>5783</v>
+      </c>
+      <c r="E1722" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1722" t="s">
+        <v>6154</v>
+      </c>
+      <c r="G1722" s="1">
+        <v>46023</v>
+      </c>
+      <c r="H1722">
+        <v>2055</v>
+      </c>
+      <c r="I1722" s="4" t="s">
+        <v>6155</v>
+      </c>
+      <c r="J1722" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1722" s="4"/>
+      <c r="L1722" s="4" t="s">
+        <v>4756</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1723" t="s">
+        <v>6156</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>6157</v>
+      </c>
+      <c r="C1723" s="4" t="s">
+        <v>3844</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1723" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1723" t="s">
+        <v>760</v>
+      </c>
+      <c r="G1723" s="1">
+        <v>47423</v>
+      </c>
+      <c r="H1723">
+        <v>354</v>
+      </c>
+      <c r="I1723" s="4" t="s">
+        <v>6158</v>
+      </c>
+      <c r="J1723" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1723" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1723" s="4" t="s">
+        <v>4725</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1724" t="s">
+        <v>6159</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>6160</v>
+      </c>
+      <c r="C1724" s="4" t="s">
+        <v>3865</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1724" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1724" t="s">
+        <v>6161</v>
+      </c>
+      <c r="G1724" s="1">
+        <v>46023</v>
+      </c>
+      <c r="H1724">
+        <v>5</v>
+      </c>
+      <c r="I1724" s="4" t="s">
+        <v>6162</v>
+      </c>
+      <c r="J1724" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1724" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1724" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1725" t="s">
+        <v>6163</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>6164</v>
+      </c>
+      <c r="C1725" s="4" t="s">
+        <v>3877</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1725" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1725" t="s">
+        <v>6165</v>
+      </c>
+      <c r="G1725" s="1">
+        <v>47331</v>
+      </c>
+      <c r="H1725">
+        <v>661</v>
+      </c>
+      <c r="I1725" s="4" t="s">
+        <v>6166</v>
+      </c>
+      <c r="J1725" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1725" s="4" t="s">
+        <v>4180</v>
+      </c>
+      <c r="L1725" s="4" t="s">
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1726" t="s">
+        <v>6167</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>6168</v>
+      </c>
+      <c r="C1726" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1726" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1726" t="s">
+        <v>6169</v>
+      </c>
+      <c r="G1726" s="1">
+        <v>46600</v>
+      </c>
+      <c r="H1726">
+        <v>1125</v>
+      </c>
+      <c r="I1726" s="4" t="s">
+        <v>6170</v>
+      </c>
+      <c r="J1726" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1726" s="4"/>
+      <c r="L1726" s="4"/>
+    </row>
+    <row r="1727" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1727" t="s">
+        <v>6171</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>6172</v>
+      </c>
+      <c r="C1727" s="4" t="s">
+        <v>3869</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1727" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1727" t="s">
+        <v>6173</v>
+      </c>
+      <c r="G1727" s="1">
+        <v>47635</v>
+      </c>
+      <c r="H1727">
+        <v>1078</v>
+      </c>
+      <c r="I1727" s="4" t="s">
+        <v>6174</v>
+      </c>
+      <c r="J1727" s="4">
+        <v>1</v>
+      </c>
+      <c r="K1727" s="4" t="s">
+        <v>4103</v>
+      </c>
+      <c r="L1727" s="4" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1728" t="s">
+        <v>6175</v>
+      </c>
+      <c r="C1728" s="4" t="s">
+        <v>3863</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1728" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1728" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1728">
+        <v>349</v>
+      </c>
+      <c r="I1728" s="4" t="s">
+        <v>6176</v>
+      </c>
+      <c r="J1728" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1728" s="4" t="s">
+        <v>4111</v>
+      </c>
+      <c r="L1728" s="4" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1729" t="s">
+        <v>6177</v>
+      </c>
+      <c r="C1729" s="4" t="s">
+        <v>3902</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1729" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1729" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1729">
+        <v>0</v>
+      </c>
+      <c r="I1729" s="4" t="s">
+        <v>6178</v>
+      </c>
+      <c r="J1729" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1729" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1729" s="4" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1730" t="s">
+        <v>6179</v>
+      </c>
+      <c r="C1730" s="4" t="s">
+        <v>6180</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>5739</v>
+      </c>
+      <c r="E1730" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1730" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="H1730">
+        <v>0</v>
+      </c>
+      <c r="I1730" s="4" t="s">
+        <v>6181</v>
+      </c>
+      <c r="J1730" s="4">
+        <v>0</v>
+      </c>
+      <c r="K1730" s="4" t="s">
+        <v>3996</v>
+      </c>
+      <c r="L1730" s="4" t="s">
+        <v>4000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
